--- a/utils/monday_sprint_sprint_2024-40.xlsx
+++ b/utils/monday_sprint_sprint_2024-40.xlsx
@@ -153,7 +153,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -3614,7 +3614,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
@@ -3634,7 +3634,7 @@
         <v>21</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -3702,7 +3702,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>41</v>

--- a/utils/monday_sprint_sprint_2024-40.xlsx
+++ b/utils/monday_sprint_sprint_2024-40.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="192">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6917925242</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>27/06/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>15/07/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>26900</t>
+    <t>7025963412</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -114,16 +114,13 @@
     <t>Média</t>
   </si>
   <si>
-    <t>15/07/2024</t>
-  </si>
-  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Julho</t>
   </si>
   <si>
-    <t>25359</t>
+    <t>6635723884</t>
   </si>
   <si>
     <t>Cores Gestão à vista Rebarbação VII</t>
@@ -132,13 +129,16 @@
     <t>14/05/2024</t>
   </si>
   <si>
+    <t>18/07/2024</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Maio</t>
   </si>
   <si>
-    <t>26087</t>
+    <t>6891515488</t>
   </si>
   <si>
     <t>WMS Almoxarifado - Programação</t>
@@ -147,13 +147,16 @@
     <t>24/06/2024</t>
   </si>
   <si>
-    <t>22418</t>
+    <t>20/07/2024</t>
+  </si>
+  <si>
+    <t>6891538454</t>
   </si>
   <si>
     <t>Tablet para o fechamento Apontamentos Moldagem ULE</t>
   </si>
   <si>
-    <t>26487</t>
+    <t>6884087518</t>
   </si>
   <si>
     <t>Correção</t>
@@ -165,13 +168,16 @@
     <t>21/06/2024</t>
   </si>
   <si>
-    <t>26389</t>
+    <t>21/07/2024</t>
+  </si>
+  <si>
+    <t>6884061139</t>
   </si>
   <si>
     <t>Controle Automático de n° sequencial de peça para ID de Bruto</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>6350546307</t>
   </si>
   <si>
     <t>Registro de Pintura (Levantamento de Dados)</t>
@@ -183,7 +189,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>26721</t>
+    <t>6973476138</t>
   </si>
   <si>
     <t>Controle na geração de Sequencias</t>
@@ -195,7 +201,7 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>26859</t>
+    <t>6980109684</t>
   </si>
   <si>
     <t>Inventário de Embalagens com Leitor Almox  (Apenas para informar saldo em estoque, sem requisição, alimentando o sistema de solicitação de embalagens)</t>
@@ -204,7 +210,7 @@
     <t>08/07/2024</t>
   </si>
   <si>
-    <t>26830</t>
+    <t>6989256613</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso - Estrutura de Dados</t>
@@ -213,19 +219,34 @@
     <t>09/07/2024</t>
   </si>
   <si>
+    <t>14/07/2024</t>
+  </si>
+  <si>
+    <t>7041953535</t>
+  </si>
+  <si>
     <t>Permitir colocar mais de uma vez o mesmo código de Evento para cada CPC</t>
   </si>
   <si>
     <t>17/07/2024</t>
   </si>
   <si>
+    <t>16/07/2024</t>
+  </si>
+  <si>
+    <t>7041956014</t>
+  </si>
+  <si>
     <t>Buscar as OTF´s de MODELO quando for selecionado Evento MODELO PRONTO</t>
   </si>
   <si>
+    <t>7041958485</t>
+  </si>
+  <si>
     <t>Consistir o Somatório dos Total dos Eventos com o Valor Total da CPC</t>
   </si>
   <si>
-    <t>25175</t>
+    <t>7073684990</t>
   </si>
   <si>
     <t>Dados Para Projeto Andon - Komatsu - Painel de gestão a vista</t>
@@ -234,46 +255,52 @@
     <t>22/07/2024</t>
   </si>
   <si>
+    <t>6973116121</t>
+  </si>
+  <si>
     <t>Melhoria Sistema de Embalagens</t>
   </si>
   <si>
-    <t>26844</t>
+    <t>6973211257</t>
   </si>
   <si>
     <t>Relatório Consumo do Material</t>
   </si>
   <si>
-    <t>26843</t>
+    <t>6973226698</t>
   </si>
   <si>
     <t>Data Planejada MPS Moldagem x Planilha MPS</t>
   </si>
   <si>
-    <t>26841</t>
+    <t>6973237945</t>
   </si>
   <si>
     <t>Ajuste tela inventario geral</t>
   </si>
   <si>
-    <t>26833</t>
+    <t>6973248761</t>
   </si>
   <si>
     <t>Alteração do estagio de fabricação</t>
   </si>
   <si>
-    <t>26832</t>
+    <t>11/07/2024</t>
+  </si>
+  <si>
+    <t>6973258101</t>
   </si>
   <si>
     <t>ocultar botão - sistema expedição</t>
   </si>
   <si>
-    <t>26813</t>
+    <t>6973298393</t>
   </si>
   <si>
     <t>Emissão de etiqueta amarela em lote</t>
   </si>
   <si>
-    <t>26805</t>
+    <t>6973309264</t>
   </si>
   <si>
     <t>[NIMBI] CRIAÇÃO DO RELATÓRIO DE MEDIÇÃO NIMBI</t>
@@ -282,172 +309,190 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>26803</t>
+    <t>6973356826</t>
   </si>
   <si>
     <t>[COMPRAS] INCLUSÃO DE DADO NO RELATÓRIO DE ENTRADAS POR ORDEM DE COMPRAS E</t>
   </si>
   <si>
-    <t>26787</t>
+    <t>6973384084</t>
   </si>
   <si>
     <t>Erro conferência de nota fiscal - múltiplos clientes no caminhão</t>
   </si>
   <si>
-    <t>26769</t>
+    <t>6973402343</t>
   </si>
   <si>
     <t>Automatização de processo de lançamento de NF Magayver</t>
   </si>
   <si>
-    <t>26762</t>
+    <t>6973410087</t>
   </si>
   <si>
     <t>RELATÓRIO COMPARAÇÃO DE VALOR OTF X PROFORMA X CPC</t>
   </si>
   <si>
-    <t>26755</t>
+    <t>10/07/2024</t>
+  </si>
+  <si>
+    <t>6973426027</t>
   </si>
   <si>
     <t>SALDO DEPÓSITO</t>
   </si>
   <si>
-    <t>26750</t>
+    <t>6973438288</t>
   </si>
   <si>
     <t>Sistema almoxarifado - exigir usuário e senha</t>
   </si>
   <si>
-    <t>26731</t>
+    <t>6973451194</t>
   </si>
   <si>
     <t>Planilha peso por área</t>
   </si>
   <si>
-    <t>26729</t>
+    <t>6973457960</t>
   </si>
   <si>
     <t>Apontamento de Retrabalho</t>
   </si>
   <si>
-    <t>26722</t>
+    <t>6973465001</t>
   </si>
   <si>
     <t>Planilha controle de corridas por forno</t>
   </si>
   <si>
-    <t>26719</t>
+    <t>6973484594</t>
   </si>
   <si>
     <t>Projeto cadeia de ajuda komatsu</t>
   </si>
   <si>
-    <t>26700</t>
+    <t>6973500120</t>
   </si>
   <si>
     <t>Imprimir Endereço - Almoxarifado</t>
   </si>
   <si>
-    <t>26694</t>
+    <t>6973509380</t>
   </si>
   <si>
     <t>Planilha MPS Pré-produtivo</t>
   </si>
   <si>
-    <t>26678</t>
+    <t>6973516337</t>
   </si>
   <si>
     <t>Coluna amostra na tela de exclusão de sequências em lote.</t>
   </si>
   <si>
-    <t>26675</t>
+    <t>6973524416</t>
   </si>
   <si>
     <t>Atualizem o banco de dados dos procedimentos de embalagem</t>
   </si>
   <si>
-    <t>26674</t>
+    <t>6973534675</t>
   </si>
   <si>
     <t>Apontamento Pintura</t>
   </si>
   <si>
-    <t>26640</t>
+    <t>6973541985</t>
   </si>
   <si>
     <t>Apontamento Pintura I</t>
   </si>
   <si>
-    <t>26637</t>
+    <t>6973548052</t>
   </si>
   <si>
     <t>Apontamento eletrônico manipuladores</t>
   </si>
   <si>
-    <t>26864</t>
+    <t>6973587054</t>
   </si>
   <si>
     <t>Controle de ensaios destrutivos em peças seriadas</t>
   </si>
   <si>
-    <t>26865</t>
+    <t>6973600274</t>
   </si>
   <si>
     <t>Ajuste PO / Gestão a vista</t>
   </si>
   <si>
-    <t>26871</t>
+    <t>6979982859</t>
   </si>
   <si>
     <t>MOVIMENTAÇÃO DE PEÇAS AMOSTRAS X PEÇAS DE PRODUÇÃO</t>
   </si>
   <si>
+    <t>6989516911</t>
+  </si>
+  <si>
     <t>Logado no manipulador pequeno, ao exportar os dados, os mesmos aparecem como “manipulador deltractor”</t>
   </si>
   <si>
+    <t>6989344588</t>
+  </si>
+  <si>
     <t>Criar opções na abertura da PO para selecionar em cada linha as opções abaixo (sugestão ser uma nova coluna)</t>
   </si>
   <si>
+    <t>6989519866</t>
+  </si>
+  <si>
     <t>Ao digitar a sequencia a ser apontada, mostrar o modelo da peça, para confirmação do operador;</t>
   </si>
   <si>
+    <t>6989373035</t>
+  </si>
+  <si>
     <t>Tela do sistema de gestão a vista</t>
   </si>
   <si>
+    <t>6989522540</t>
+  </si>
+  <si>
     <t>Estratificar separadamente as paradas apontadas ao longo do turno. (Estão aparecendo agrupadas);</t>
   </si>
   <si>
+    <t>6989542414</t>
+  </si>
+  <si>
     <t>Apontar mais de uma sequencia em um ciclo (algumas peças do mesmo modelo, possuem sequencias diferentes e são processadas simultaneamente</t>
   </si>
   <si>
-    <t>26868</t>
+    <t>7000497378</t>
   </si>
   <si>
     <t>Bug criação de etiqueta</t>
   </si>
   <si>
-    <t>10/07/2024</t>
-  </si>
-  <si>
-    <t>26899</t>
+    <t>7025954086</t>
   </si>
   <si>
     <t>Melhoria Sistemas de Custeio - APOIO TRATAMENTO TÉRMICO</t>
   </si>
   <si>
-    <t>26901</t>
+    <t>7025970668</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Extração Custeio INSPEÇÃO</t>
   </si>
   <si>
-    <t>26902</t>
+    <t>7025982094</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Extração Custeio USINAGEM</t>
   </si>
   <si>
-    <t>26903</t>
+    <t>7025996188</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Extração Custeio ACABAMENTO</t>
@@ -459,7 +504,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-40</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1101,7 +1146,7 @@
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>24</v>
@@ -1113,45 +1158,45 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1198,7 +1243,7 @@
         <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1215,7 +1260,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1227,10 +1272,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1245,7 +1290,7 @@
         <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1262,22 +1307,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>32</v>
@@ -1289,10 +1334,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1301,7 +1346,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1309,38 +1354,38 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1348,7 +1393,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1356,7 +1401,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1368,10 +1413,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
@@ -1383,10 +1428,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1398,12 +1443,12 @@
         <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1415,10 +1460,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -1430,10 +1475,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1442,15 +1487,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1462,10 +1507,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
@@ -1477,7 +1522,7 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>24</v>
@@ -1492,12 +1537,12 @@
         <v>39</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1509,10 +1554,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>32</v>
@@ -1524,10 +1569,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1539,12 +1584,12 @@
         <v>39</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1556,10 +1601,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1571,10 +1616,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1583,15 +1628,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1603,10 +1648,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1618,10 +1663,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1630,15 +1675,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1650,10 +1695,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>32</v>
@@ -1665,10 +1710,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1677,15 +1722,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1697,10 +1742,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>32</v>
@@ -1712,10 +1757,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1727,42 +1772,42 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1771,15 +1816,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1791,10 +1836,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -1806,10 +1851,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1818,30 +1863,30 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>32</v>
@@ -1853,10 +1898,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1865,30 +1910,30 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
@@ -1900,10 +1945,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1912,15 +1957,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1932,10 +1977,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>32</v>
@@ -1947,10 +1992,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1959,15 +2004,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1979,10 +2024,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>32</v>
@@ -1994,10 +2039,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2006,15 +2051,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2026,10 +2071,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>32</v>
@@ -2041,10 +2086,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2053,15 +2098,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2073,13 +2118,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -2088,10 +2133,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2100,15 +2145,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2120,13 +2165,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2135,10 +2180,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2147,30 +2192,30 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>32</v>
@@ -2182,10 +2227,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2194,15 +2239,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2214,10 +2259,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>32</v>
@@ -2229,10 +2274,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2241,15 +2286,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2261,10 +2306,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -2276,10 +2321,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2288,15 +2333,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2308,10 +2353,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -2323,10 +2368,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2335,15 +2380,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2355,10 +2400,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -2370,10 +2415,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2382,15 +2427,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2402,10 +2447,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -2417,10 +2462,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2429,15 +2474,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2449,10 +2494,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>32</v>
@@ -2464,10 +2509,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2476,15 +2521,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2496,10 +2541,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>32</v>
@@ -2511,10 +2556,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2523,15 +2568,15 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2543,10 +2588,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>32</v>
@@ -2558,10 +2603,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2570,15 +2615,15 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2590,10 +2635,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>32</v>
@@ -2605,10 +2650,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2617,15 +2662,15 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2637,10 +2682,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>32</v>
@@ -2652,10 +2697,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2664,15 +2709,15 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2684,10 +2729,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>32</v>
@@ -2699,10 +2744,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2711,15 +2756,15 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2731,10 +2776,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>32</v>
@@ -2746,10 +2791,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2758,15 +2803,15 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2778,10 +2823,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>32</v>
@@ -2793,10 +2838,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2805,15 +2850,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2825,10 +2870,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -2840,10 +2885,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2852,15 +2897,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2872,10 +2917,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>32</v>
@@ -2887,10 +2932,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2899,15 +2944,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2919,10 +2964,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>32</v>
@@ -2934,10 +2979,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2946,15 +2991,15 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2966,10 +3011,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>32</v>
@@ -2981,10 +3026,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2993,15 +3038,15 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3013,10 +3058,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>32</v>
@@ -3028,10 +3073,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3043,12 +3088,12 @@
         <v>39</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3060,10 +3105,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>32</v>
@@ -3075,10 +3120,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3090,12 +3135,12 @@
         <v>39</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3107,10 +3152,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>32</v>
@@ -3122,10 +3167,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3137,12 +3182,12 @@
         <v>39</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3154,10 +3199,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>32</v>
@@ -3169,10 +3214,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3184,12 +3229,12 @@
         <v>39</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3201,10 +3246,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>32</v>
@@ -3216,10 +3261,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3231,12 +3276,12 @@
         <v>39</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3248,10 +3293,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>32</v>
@@ -3263,10 +3308,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3278,12 +3323,12 @@
         <v>39</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3295,10 +3340,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>32</v>
@@ -3310,10 +3355,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3325,27 +3370,27 @@
         <v>39</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>32</v>
@@ -3357,10 +3402,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3372,12 +3417,12 @@
         <v>39</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3389,10 +3434,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>32</v>
@@ -3404,7 +3449,7 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>24</v>
@@ -3416,15 +3461,15 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3436,10 +3481,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>32</v>
@@ -3451,7 +3496,7 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>24</v>
@@ -3463,15 +3508,15 @@
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3483,10 +3528,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>32</v>
@@ -3498,7 +3543,7 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>24</v>
@@ -3510,15 +3555,15 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3530,10 +3575,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>32</v>
@@ -3545,7 +3590,7 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>24</v>
@@ -3557,10 +3602,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3576,23 +3621,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3600,16 +3645,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3620,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3628,7 +3673,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3641,7 +3686,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3649,7 +3694,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3680,12 +3725,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B2">
         <v>54</v>
@@ -3699,7 +3744,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3709,25 +3754,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3744,13 +3789,13 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3762,15 +3807,15 @@
         <v>54</v>
       </c>
       <c r="P10" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="Q10">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -3788,16 +3833,16 @@
         <v>54</v>
       </c>
       <c r="M11" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q11">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3814,53 +3859,47 @@
         <v>50</v>
       </c>
       <c r="J12" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Q12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13">
-        <v>5</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3868,7 +3907,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3876,7 +3915,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3884,7 +3923,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3892,10 +3931,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3903,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3911,142 +3950,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
